--- a/artfynd/A 320-2026 artfynd.xlsx
+++ b/artfynd/A 320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129425325</v>
+        <v>129425399</v>
       </c>
       <c r="B2" t="n">
-        <v>80186</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470436</v>
+        <v>470461</v>
       </c>
       <c r="R2" t="n">
-        <v>6868500</v>
+        <v>6868473</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,57 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425578</v>
+        <v>129425923</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Bodsjön, Väster-Bodsjön, Hjd</t>
+          <t>Gröningsån, Gröningsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470448</v>
+        <v>470271</v>
       </c>
       <c r="R3" t="n">
-        <v>6868416</v>
+        <v>6868533</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425344</v>
+        <v>129425592</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470437</v>
+        <v>470462</v>
       </c>
       <c r="R4" t="n">
-        <v>6868500</v>
+        <v>6868444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129425399</v>
+        <v>129425262</v>
       </c>
       <c r="B5" t="n">
-        <v>79113</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470461</v>
+        <v>470431</v>
       </c>
       <c r="R5" t="n">
-        <v>6868473</v>
+        <v>6868560</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129425262</v>
+        <v>129425912</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Bodsjön, Väster-Bodsjön, Hjd</t>
+          <t>Gröningsån, Gröningsån, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470431</v>
+        <v>470283</v>
       </c>
       <c r="R6" t="n">
-        <v>6868560</v>
+        <v>6868530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129425366</v>
+        <v>129425325</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470465</v>
+        <v>470436</v>
       </c>
       <c r="R7" t="n">
-        <v>6868498</v>
+        <v>6868500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129425592</v>
+        <v>129425366</v>
       </c>
       <c r="B8" t="n">
-        <v>80187</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470462</v>
+        <v>470465</v>
       </c>
       <c r="R8" t="n">
-        <v>6868444</v>
+        <v>6868498</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129425466</v>
+        <v>129425408</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470453</v>
+        <v>470464</v>
       </c>
       <c r="R9" t="n">
-        <v>6868457</v>
+        <v>6868464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129425923</v>
+        <v>129425466</v>
       </c>
       <c r="B10" t="n">
-        <v>78747</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gröningsån, Gröningsån, Hjd</t>
+          <t>Väster-Bodsjön, Väster-Bodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470271</v>
+        <v>470453</v>
       </c>
       <c r="R10" t="n">
-        <v>6868533</v>
+        <v>6868457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,45 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129425912</v>
+        <v>129425344</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gröningsån, Gröningsån, Hjd</t>
+          <t>Väster-Bodsjön, Väster-Bodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470283</v>
+        <v>470437</v>
       </c>
       <c r="R11" t="n">
-        <v>6868530</v>
+        <v>6868500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1642,112 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129425578</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Väster-Bodsjön, Väster-Bodsjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>470448</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6868416</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 320-2026 artfynd.xlsx
+++ b/artfynd/A 320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425923</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425262</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425912</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425325</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425366</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425408</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425466</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425344</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,8 +1803,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>